--- a/test/generator/baseline/gen.odt.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.odt.to.xlsx.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Tables 4" sheetId="4" r:id="rId4"/>
     <sheet name="Tables 5" sheetId="5" r:id="rId5"/>
     <sheet name="Text" sheetId="6" r:id="rId6"/>
+    <sheet name="Notes" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -325,8 +326,10 @@
       <c r="C3">
         <v>103</v>
       </c>
-      <c r="D3">
-        <v>7</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+7</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -364,8 +367,10 @@
       <c r="C6">
         <v>20</v>
       </c>
-      <c r="D6">
-        <v>4</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+4</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1176,4 +1181,39 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Footnote 1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In paged media, footnotes are usually displayed at the bottom of the text. However, in ebooks, a better paradigm is to make them clickable endnotes that the user can browse at her pleasure. This conversion is handled automatically by calibre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Endnote 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Endnotes are typically used for longer notes, they remain endnotes when converted into ebook form, except that they have an additional backlink to make it easy to return to the current position after reading the note.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/test/generator/baseline/gen.odt.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.odt.to.xlsx.xlsx
@@ -804,7 +804,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footnotes and endnotes are automatically recognized and both are converted to endnotes, with backlinks for maximum ease of use in ebook devices.</t>
+          <t xml:space="preserve">Footnotes [Footnote 1] and endnotes [Endnote 1] are automatically recognized and both are converted to endnotes, with backlinks for maximum ease of use in ebook devices.</t>
         </is>
       </c>
     </row>
@@ -986,196 +986,203 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t xml:space="preserve">165 Inspirational Quotes To Keep You Motivated In Life</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t xml:space="preserve">There is no analogous technology in ebooks, so the conversion will usually end up placing the image either centered or floating close to the point in the text where it was inserted, not necessarily where it appears on the page in Word.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Lists</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t xml:space="preserve">All types of lists are supported by the conversion, with the exception of lists that use fancy bullets, these get converted to regular bullets.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bulleted List</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">• One</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Two</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Numbered List</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">1. One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Two</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Multi-level Lists</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">1. One</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three</t>
+          <t xml:space="preserve">1.1. Two</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
+          <t xml:space="preserve">1.1.1. Three</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">1.1.2. Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Six</t>
+          <t xml:space="preserve">1.1.3. Five</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Multi-level list with bullets:</t>
+          <t xml:space="preserve">2. Six</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">A Multi-level list with bullets:</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">▪ One</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bullet uses an image as the bullet item</t>
+          <t xml:space="preserve">• Two</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">• This bullet uses an image as the bullet item</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">◦ Four</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▪ Five</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Continued Lists</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">i. One</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">An interruption in our regularly scheduled listing, for this essential and very relevant public service announcement.</t>
+          <t xml:space="preserve">ii. Two</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">We now resume our normal programming</t>
+          <t xml:space="preserve">An interruption in our regularly scheduled listing, for this essential and very relevant public service announcement.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">iii. We now resume our normal programming</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iv. Four</t>
         </is>
       </c>
     </row>

--- a/test/generator/baseline/gen.odt.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.odt.to.xlsx.xlsx
@@ -1187,6 +1187,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A29" r:id="rId1"/>
+  </hyperlinks>
 </worksheet>
 </file>
 

--- a/test/generator/baseline/gen.odt.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.odt.to.xlsx.xlsx
@@ -450,7 +450,6 @@
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
   </cols>
   <sheetData>
